--- a/InputData/indst/FLRbI/Foreign Leakage Rate by Industry.xlsx
+++ b/InputData/indst/FLRbI/Foreign Leakage Rate by Industry.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28830"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\indst\FLRbI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789840D7-2404-480A-8F40-C7CD3E312472}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789840D7-2404-480A-8F40-C7CD3E312472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3915" yWindow="1065" windowWidth="23805" windowHeight="15630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,8 +17,11 @@
     <sheet name="SourceData" sheetId="2" r:id="rId2"/>
     <sheet name="FLRbI" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -26,6 +29,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,6 +40,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="113">
   <si>
+    <t>FLRbI Foreign Leakage Rate by Industry</t>
+  </si>
+  <si>
     <t>Source:</t>
   </si>
   <si>
@@ -50,19 +58,226 @@
     <t>Page 83, Table 15</t>
   </si>
   <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>For every unit of CO2e not emitted in this country as a result of the modeled policy package, a fraction</t>
+  </si>
+  <si>
+    <t>of a unit of CO2e is emitted in a foreign country. This may be due to businesses relocating or opening</t>
+  </si>
+  <si>
+    <t>elsewhere rather than in this country, or it may be due to changes in production levels of existing</t>
+  </si>
+  <si>
+    <t>businesses. These leakage rates were determined via a computer model based on a carbon tax, so</t>
+  </si>
+  <si>
+    <t>leakage can be negative if a foreign firm has a lower carbon intensity than a U.S. firm when</t>
+  </si>
+  <si>
+    <t>producing a particular good (this is the case for natural gas and coal), or if imports to the U.S. are</t>
+  </si>
+  <si>
+    <t>reduced (this is the case for oil).</t>
+  </si>
+  <si>
+    <t>We assume zero leakage for water and waste, which is primarily water treatment and cannot be offshored.</t>
+  </si>
+  <si>
+    <t>How to Interpret Leakage Components from the RFF Table</t>
+  </si>
+  <si>
+    <t>Change in U.S. Emissions</t>
+  </si>
+  <si>
+    <t>This is always negative.  This is the reduction in U.S. emissions from a sector in response to</t>
+  </si>
+  <si>
+    <t>a $15/ton carbon price.  For our purposes, we are only looking at rebound magnitudes in</t>
+  </si>
+  <si>
+    <t>foreign countries per unit abatement in the U.S., so the specific amount of abatement in</t>
+  </si>
+  <si>
+    <t>the U.S. (or the $15/ton carbon tax that caused it) are not directly relevant.</t>
+  </si>
+  <si>
+    <t>(However, it does mean we are taking a point estimate, as we do for elasticities, when</t>
+  </si>
+  <si>
+    <t>leakage really would be described by a nonlinear function.)</t>
+  </si>
+  <si>
+    <t>Due to higher exports to U.S.</t>
+  </si>
+  <si>
+    <t>This reflects increased production of goods overseas, for export to the U.S. (to make up</t>
+  </si>
+  <si>
+    <t>for part of the reduction in goods produced within the U.S.)</t>
+  </si>
+  <si>
+    <t>In the case of fuels (wood, coal, oil, and gas) and certain types of equipment</t>
+  </si>
+  <si>
+    <t>(transportation equipment, electronic equipment, machinery), this value is negative.</t>
+  </si>
+  <si>
+    <t>Fuels would be subject to a carbon tax whether produced domestically or imported, so</t>
+  </si>
+  <si>
+    <t>importing these fuels does not avoid the carbon tax, hence no additional imports are</t>
+  </si>
+  <si>
+    <t>stimulated.  Equipment that generates emissions when used may also have reduced</t>
+  </si>
+  <si>
+    <t>demand for imports to the U.S.</t>
+  </si>
+  <si>
+    <t>Due to lower imports from U.S.</t>
+  </si>
+  <si>
+    <t>Some goods that previously were exported from the U.S. to other countries are diverted</t>
+  </si>
+  <si>
+    <t>to be used domestically within the U.S.  This results in positive values in this column.</t>
+  </si>
+  <si>
+    <t>Negative values indicate in increase in exports from the U.S. to other countries, which</t>
+  </si>
+  <si>
+    <t>happens for the fossil fuels (coal, oil, and gas), because exporting them avoids the carbon</t>
+  </si>
+  <si>
+    <t>tax, and machinery, whose use consumes energy and generates emissions.</t>
+  </si>
+  <si>
+    <t>Due to differences in Carbon Intensity</t>
+  </si>
+  <si>
+    <t>In manufacturing industries, when the U.S. produces less emissions, it uses less fuel.</t>
+  </si>
+  <si>
+    <t>The reduction in demand for fuel by the U.S. causes global fuel prices to go down.</t>
+  </si>
+  <si>
+    <t>Other countries use more fuel as a result.  This increases the "carbon intensity" of</t>
+  </si>
+  <si>
+    <t>their economies.  This is the effect being captured in this column.</t>
+  </si>
+  <si>
+    <t>Note that the values in this column are negative for some fossil fuel extraction industries</t>
+  </si>
+  <si>
+    <t>(coal and gas mining).  This is because when the U.S. reduces production</t>
+  </si>
+  <si>
+    <t>of these goods, the global price of these fuels goes up rather than down,</t>
+  </si>
+  <si>
+    <t>because the reduced supply (from the drop in U.S. production) drives up prices.</t>
+  </si>
+  <si>
+    <t>This reduction in supply is a more important effect than the reduction in U.S.</t>
+  </si>
+  <si>
+    <t>usage of fossil fuels in the extraction industries, to power their operations,</t>
+  </si>
+  <si>
+    <t>which (as with the manufacturing industries) has a tendency to reduce global</t>
+  </si>
+  <si>
+    <t>fuel prices.  So on balance, reducing U.S. production of fossil fuels reduces the</t>
+  </si>
+  <si>
+    <t>carbon intensity of foreign economies.</t>
+  </si>
+  <si>
+    <t>Change in non-Annex I emissions due to change in net exports to U.S. (1000 tons CO2)</t>
+  </si>
+  <si>
+    <t>Due to higher exports to US</t>
+  </si>
+  <si>
+    <t>Due to lower imports from US</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Leakage Rate</t>
+  </si>
+  <si>
+    <t>Food, Beverages, and Tobacco</t>
+  </si>
+  <si>
     <t>Textiles</t>
   </si>
   <si>
+    <t>Wearing Apparel and Leather</t>
+  </si>
+  <si>
     <t>Wood</t>
   </si>
   <si>
+    <t>Paper and Publishing</t>
+  </si>
+  <si>
+    <t>Petroleum and Coal Products</t>
+  </si>
+  <si>
+    <t>Chemicals, Rubber, and Plastics</t>
+  </si>
+  <si>
+    <t>Non-Metallic Mineral Products</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
+    <t>Nonferrous primary metals</t>
+  </si>
+  <si>
+    <t>Fabricated Metal Products</t>
+  </si>
+  <si>
+    <t>Transportation Equipment</t>
+  </si>
+  <si>
+    <t>Electronic equipment</t>
+  </si>
+  <si>
+    <t>Machinery</t>
+  </si>
+  <si>
+    <t>Other Manufacturing</t>
+  </si>
+  <si>
+    <t>We take an average of other manufacturing categories here to avoid an unrealistic outlier (170.5% leakage rate)</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
     <t>Coal</t>
   </si>
   <si>
-    <t>Machinery</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
+    <t>Oil mining</t>
+  </si>
+  <si>
+    <t>Gas mining</t>
+  </si>
+  <si>
+    <t>Other Minerals</t>
+  </si>
+  <si>
+    <t>Electric Utilities</t>
+  </si>
+  <si>
+    <t>Gas manuf. and distribution</t>
   </si>
   <si>
     <t>Construction</t>
@@ -71,223 +286,22 @@
     <t>Trade</t>
   </si>
   <si>
+    <t>Transportation Services</t>
+  </si>
+  <si>
     <t>Communications</t>
   </si>
   <si>
-    <t>Food, Beverages, and Tobacco</t>
-  </si>
-  <si>
-    <t>Wearing Apparel and Leather</t>
-  </si>
-  <si>
-    <t>Paper and Publishing</t>
-  </si>
-  <si>
-    <t>Petroleum and Coal Products</t>
-  </si>
-  <si>
-    <t>Chemicals, Rubber, and Plastics</t>
-  </si>
-  <si>
-    <t>Non-Metallic Mineral Products</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Nonferrous primary metals</t>
-  </si>
-  <si>
-    <t>Fabricated Metal Products</t>
-  </si>
-  <si>
-    <t>Transportation Equipment</t>
-  </si>
-  <si>
-    <t>Electronic equipment</t>
-  </si>
-  <si>
-    <t>Other Manufacturing</t>
-  </si>
-  <si>
-    <t>Oil mining</t>
-  </si>
-  <si>
-    <t>Gas mining</t>
-  </si>
-  <si>
-    <t>Other Minerals</t>
-  </si>
-  <si>
-    <t>Electric Utilities</t>
-  </si>
-  <si>
-    <t>Gas manuf. and distribution</t>
-  </si>
-  <si>
-    <t>Transportation Services</t>
-  </si>
-  <si>
     <t>Finance and Insurance</t>
   </si>
   <si>
     <t>Services (inc real estate)</t>
   </si>
   <si>
-    <t>Change in U.S. Emissions</t>
-  </si>
-  <si>
-    <t>Due to higher exports to US</t>
-  </si>
-  <si>
-    <t>Due to lower imports from US</t>
-  </si>
-  <si>
-    <t>Due to differences in Carbon Intensity</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Change in non-Annex I emissions due to change in net exports to U.S. (1000 tons CO2)</t>
-  </si>
-  <si>
-    <t>Leakage Rate</t>
-  </si>
-  <si>
     <t>The numbers in this table are based on a $15/ton CO2 tax in Annex I Countries.</t>
   </si>
   <si>
-    <t>FLRbI Foreign Leakage Rate by Industry</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>This is always negative.  This is the reduction in U.S. emissions from a sector in response to</t>
-  </si>
-  <si>
-    <t>a $15/ton carbon price.  For our purposes, we are only looking at rebound magnitudes in</t>
-  </si>
-  <si>
-    <t>foreign countries per unit abatement in the U.S., so the specific amount of abatement in</t>
-  </si>
-  <si>
-    <t>the U.S. (or the $15/ton carbon tax that caused it) are not directly relevant.</t>
-  </si>
-  <si>
-    <t>(However, it does mean we are taking a point estimate, as we do for elasticities, when</t>
-  </si>
-  <si>
-    <t>leakage really would be described by a nonlinear function.)</t>
-  </si>
-  <si>
-    <t>Due to higher exports to U.S.</t>
-  </si>
-  <si>
-    <t>In manufacturing industries, when the U.S. produces less emissions, it uses less fuel.</t>
-  </si>
-  <si>
-    <t>The reduction in demand for fuel by the U.S. causes global fuel prices to go down.</t>
-  </si>
-  <si>
-    <t>Other countries use more fuel as a result.  This increases the "carbon intensity" of</t>
-  </si>
-  <si>
-    <t>their economies.  This is the effect being captured in this column.</t>
-  </si>
-  <si>
-    <t>because the reduced supply (from the drop in U.S. production) drives up prices.</t>
-  </si>
-  <si>
-    <t>This reduction in supply is a more important effect than the reduction in U.S.</t>
-  </si>
-  <si>
-    <t>usage of fossil fuels in the extraction industries, to power their operations,</t>
-  </si>
-  <si>
-    <t>which (as with the manufacturing industries) has a tendency to reduce global</t>
-  </si>
-  <si>
-    <t>fuel prices.  So on balance, reducing U.S. production of fossil fuels reduces the</t>
-  </si>
-  <si>
-    <t>carbon intensity of foreign economies.</t>
-  </si>
-  <si>
-    <t>of these goods, the global price of these fuels goes up rather than down,</t>
-  </si>
-  <si>
-    <t>Note that the values in this column are negative for some fossil fuel extraction industries</t>
-  </si>
-  <si>
-    <t>(coal and gas mining).  This is because when the U.S. reduces production</t>
-  </si>
-  <si>
-    <t>This reflects increased production of goods overseas, for export to the U.S. (to make up</t>
-  </si>
-  <si>
-    <t>for part of the reduction in goods produced within the U.S.)</t>
-  </si>
-  <si>
-    <t>In the case of fuels (wood, coal, oil, and gas) and certain types of equipment</t>
-  </si>
-  <si>
-    <t>(transportation equipment, electronic equipment, machinery), this value is negative.</t>
-  </si>
-  <si>
-    <t>Fuels would be subject to a carbon tax whether produced domestically or imported, so</t>
-  </si>
-  <si>
-    <t>importing these fuels does not avoid the carbon tax, hence no additional imports are</t>
-  </si>
-  <si>
-    <t>stimulated.  Equipment that generates emissions when used may also have reduced</t>
-  </si>
-  <si>
-    <t>demand for imports to the U.S.</t>
-  </si>
-  <si>
-    <t>Due to lower imports from U.S.</t>
-  </si>
-  <si>
-    <t>Some goods that previously were exported from the U.S. to other countries are diverted</t>
-  </si>
-  <si>
-    <t>to be used domestically within the U.S.  This results in positive values in this column.</t>
-  </si>
-  <si>
-    <t>Negative values indicate in increase in exports from the U.S. to other countries, which</t>
-  </si>
-  <si>
-    <t>happens for the fossil fuels (coal, oil, and gas), because exporting them avoids the carbon</t>
-  </si>
-  <si>
-    <t>tax, and machinery, whose use consumes energy and generates emissions.</t>
-  </si>
-  <si>
-    <t>How to Interpret Leakage Components from the RFF Table</t>
-  </si>
-  <si>
-    <t>For every unit of CO2e not emitted in this country as a result of the modeled policy package, a fraction</t>
-  </si>
-  <si>
-    <t>of a unit of CO2e is emitted in a foreign country. This may be due to businesses relocating or opening</t>
-  </si>
-  <si>
-    <t>elsewhere rather than in this country, or it may be due to changes in production levels of existing</t>
-  </si>
-  <si>
-    <t>businesses. These leakage rates were determined via a computer model based on a carbon tax, so</t>
-  </si>
-  <si>
-    <t>leakage can be negative if a foreign firm has a lower carbon intensity than a U.S. firm when</t>
-  </si>
-  <si>
-    <t>producing a particular good (this is the case for natural gas and coal), or if imports to the U.S. are</t>
-  </si>
-  <si>
-    <t>reduced (this is the case for oil).</t>
+    <t>Unit: dimensionless</t>
   </si>
   <si>
     <t>agriculture and forestry 01T03</t>
@@ -363,15 +377,6 @@
   </si>
   <si>
     <t>construction 41T43</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless</t>
-  </si>
-  <si>
-    <t>We assume zero leakage for water and waste, which is primarily water treatment and cannot be offshored.</t>
-  </si>
-  <si>
-    <t>We take an average of other manufacturing categories here to avoid an unrealistic outlier (170.5% leakage rate)</t>
   </si>
 </sst>
 </file>
@@ -382,7 +387,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,7 +470,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -481,7 +486,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -491,14 +495,13 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -519,9 +522,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -559,9 +562,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -594,26 +597,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -646,26 +632,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -840,281 +809,278 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="34.42578125" customWidth="1"/>
     <col min="3" max="3" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="B4" s="2">
         <v>2010</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" s="1"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="B27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="B31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="B32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="B34" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="B35" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="B36" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="B37" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="B38" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="B41" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
+    <row r="42" spans="1:2">
+      <c r="B42" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="B43" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="B44" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="B45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="B48" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
+    <row r="54" spans="2:2">
+      <c r="B54" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
+    <row r="55" spans="2:2">
+      <c r="B55" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
+    <row r="56" spans="2:2">
+      <c r="B56" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
+    <row r="57" spans="2:2">
+      <c r="B57" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
+    <row r="58" spans="2:2">
+      <c r="B58" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+    <row r="59" spans="2:2">
+      <c r="B59" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B41" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B42" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B43" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B45" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B48" t="s">
+    <row r="60" spans="2:2">
+      <c r="B60" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" t="s">
+    <row r="61" spans="2:2">
+      <c r="B61" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B53" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B56" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B57" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B58" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B59" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B60" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B61" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1129,7 +1095,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.28515625" customWidth="1"/>
     <col min="2" max="3" width="15.140625" customWidth="1"/>
@@ -1137,40 +1103,40 @@
     <col min="5" max="5" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="14"/>
+    <row r="1" spans="1:7" ht="30" customHeight="1">
+      <c r="B1" s="13"/>
       <c r="C1" s="17" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D1" s="17"/>
       <c r="E1" s="17"/>
       <c r="F1" s="18"/>
     </row>
-    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B2" s="15" t="s">
-        <v>33</v>
+    <row r="2" spans="1:7" ht="30">
+      <c r="B2" s="14" t="s">
+        <v>16</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>55</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="16">
+        <v>57</v>
+      </c>
+      <c r="B3" s="15">
         <v>-7457</v>
       </c>
       <c r="C3">
@@ -1182,19 +1148,19 @@
       <c r="E3">
         <v>5</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="13">
         <v>22</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="12">
         <f t="shared" ref="G3:G17" si="0">-F3/B3</f>
         <v>2.9502480890438512E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="14">
+        <v>58</v>
+      </c>
+      <c r="B4" s="13">
         <v>-623</v>
       </c>
       <c r="C4">
@@ -1206,19 +1172,19 @@
       <c r="E4">
         <v>12</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="13">
         <v>26</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <f t="shared" si="0"/>
         <v>4.1733547351524881E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="14">
+        <v>59</v>
+      </c>
+      <c r="B5" s="13">
         <v>-317</v>
       </c>
       <c r="C5">
@@ -1230,19 +1196,19 @@
       <c r="E5">
         <v>26</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="13">
         <v>30</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <f t="shared" si="0"/>
         <v>9.4637223974763401E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="14">
+        <v>60</v>
+      </c>
+      <c r="B6" s="13">
         <v>-889</v>
       </c>
       <c r="C6">
@@ -1254,19 +1220,19 @@
       <c r="E6">
         <v>-9</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="13">
         <v>-16</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="12">
         <f t="shared" si="0"/>
         <v>-1.799775028121485E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="16">
+        <v>61</v>
+      </c>
+      <c r="B7" s="15">
         <v>-7933</v>
       </c>
       <c r="C7">
@@ -1278,19 +1244,19 @@
       <c r="E7">
         <v>35</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="13">
         <v>79</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="12">
         <f t="shared" si="0"/>
         <v>9.958401613513173E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="16">
+        <v>62</v>
+      </c>
+      <c r="B8" s="15">
         <v>-18447</v>
       </c>
       <c r="C8">
@@ -1302,19 +1268,19 @@
       <c r="E8">
         <v>701</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <v>1522</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="12">
         <f t="shared" si="0"/>
         <v>8.2506640646175536E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="16">
+        <v>63</v>
+      </c>
+      <c r="B9" s="15">
         <v>-14947</v>
       </c>
       <c r="C9">
@@ -1326,19 +1292,19 @@
       <c r="E9" s="4">
         <v>2726</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="15">
         <v>3955</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="12">
         <f t="shared" si="0"/>
         <v>0.26460159229276781</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="16">
+        <v>64</v>
+      </c>
+      <c r="B10" s="15">
         <v>-10110</v>
       </c>
       <c r="C10">
@@ -1350,19 +1316,19 @@
       <c r="E10">
         <v>683</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="13">
         <v>961</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="12">
         <f t="shared" si="0"/>
         <v>9.50544015825915E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="16">
+        <v>65</v>
+      </c>
+      <c r="B11" s="15">
         <v>-4616</v>
       </c>
       <c r="C11">
@@ -1374,19 +1340,19 @@
       <c r="E11">
         <v>399</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="13">
         <v>691</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="12">
         <f t="shared" si="0"/>
         <v>0.14969670710571925</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="16">
+        <v>66</v>
+      </c>
+      <c r="B12" s="15">
         <v>-1821</v>
       </c>
       <c r="C12">
@@ -1398,19 +1364,19 @@
       <c r="E12">
         <v>68</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="13">
         <v>245</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="12">
         <f t="shared" si="0"/>
         <v>0.13454146073585943</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="16">
+        <v>67</v>
+      </c>
+      <c r="B13" s="15">
         <v>-1010</v>
       </c>
       <c r="C13">
@@ -1422,19 +1388,19 @@
       <c r="E13">
         <v>9</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="13">
         <v>12</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <f t="shared" si="0"/>
         <v>1.1881188118811881E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="16">
+        <v>68</v>
+      </c>
+      <c r="B14" s="15">
         <v>-1434</v>
       </c>
       <c r="C14">
@@ -1446,19 +1412,19 @@
       <c r="E14">
         <v>6</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="13">
         <v>7</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="12">
         <f t="shared" si="0"/>
         <v>4.8814504881450485E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="14">
+        <v>69</v>
+      </c>
+      <c r="B15" s="13">
         <v>-572</v>
       </c>
       <c r="C15">
@@ -1470,19 +1436,19 @@
       <c r="E15">
         <v>79</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="13">
         <v>76</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="12">
         <f t="shared" si="0"/>
         <v>0.13286713286713286</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="16">
+        <v>70</v>
+      </c>
+      <c r="B16" s="15">
         <v>-1496</v>
       </c>
       <c r="C16">
@@ -1494,19 +1460,19 @@
       <c r="E16">
         <v>18</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="13">
         <v>3</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="12">
         <f t="shared" si="0"/>
         <v>2.0053475935828879E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="14">
+        <v>71</v>
+      </c>
+      <c r="B17" s="13">
         <v>-183</v>
       </c>
       <c r="C17">
@@ -1518,22 +1484,22 @@
       <c r="E17">
         <v>305</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="13">
         <v>312</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="16">
         <f>AVERAGE(G3:G16)</f>
         <v>7.2094113727029757E-2</v>
       </c>
       <c r="H17" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="16">
+        <v>73</v>
+      </c>
+      <c r="B18" s="15">
         <v>-3229</v>
       </c>
       <c r="C18">
@@ -1545,19 +1511,19 @@
       <c r="E18">
         <v>-5</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="13">
         <v>19</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="12">
         <f>-F18/B18</f>
         <v>5.884174667079591E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="14">
+        <v>74</v>
+      </c>
+      <c r="B19" s="13">
         <v>-510</v>
       </c>
       <c r="C19">
@@ -1569,19 +1535,19 @@
       <c r="E19">
         <v>-92</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="13">
         <v>-107</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="12">
         <f t="shared" ref="G19:G30" si="1">-F19/B19</f>
         <v>-0.20980392156862746</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="16">
+        <v>75</v>
+      </c>
+      <c r="B20" s="15">
         <v>-2088</v>
       </c>
       <c r="C20" s="4">
@@ -1593,19 +1559,19 @@
       <c r="E20">
         <v>828</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="15">
         <v>-1314</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="12">
         <f t="shared" si="1"/>
         <v>-0.62931034482758619</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="14">
+        <v>76</v>
+      </c>
+      <c r="B21" s="13">
         <v>-428</v>
       </c>
       <c r="C21">
@@ -1617,19 +1583,19 @@
       <c r="E21">
         <v>-613</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="13">
         <v>-839</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="12">
         <f t="shared" si="1"/>
         <v>-1.9602803738317758</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="14">
+        <v>77</v>
+      </c>
+      <c r="B22" s="13">
         <v>-11</v>
       </c>
       <c r="C22">
@@ -1641,19 +1607,19 @@
       <c r="E22">
         <v>9</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="13">
         <v>9</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="12">
         <f t="shared" si="1"/>
         <v>0.81818181818181823</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="16">
+        <v>78</v>
+      </c>
+      <c r="B23" s="15">
         <v>-411572</v>
       </c>
       <c r="C23">
@@ -1665,19 +1631,19 @@
       <c r="E23">
         <v>227</v>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="15">
         <v>1263</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="12">
         <f t="shared" si="1"/>
         <v>3.0687218761237403E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="16">
+        <v>79</v>
+      </c>
+      <c r="B24" s="15">
         <v>-6542</v>
       </c>
       <c r="C24">
@@ -1689,19 +1655,19 @@
       <c r="E24">
         <v>10</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="13">
         <v>10</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="12">
         <f t="shared" si="1"/>
         <v>1.5285845307245491E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="14">
+        <v>80</v>
+      </c>
+      <c r="B25" s="13">
         <v>-881</v>
       </c>
       <c r="C25">
@@ -1713,19 +1679,19 @@
       <c r="E25">
         <v>0</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="13">
         <v>0</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" s="16">
+        <v>81</v>
+      </c>
+      <c r="B26" s="15">
         <v>-5443</v>
       </c>
       <c r="C26">
@@ -1737,19 +1703,19 @@
       <c r="E26">
         <v>-2</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F26" s="13">
         <v>-4</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="12">
         <f t="shared" si="1"/>
         <v>-7.3488884806173071E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="16">
+        <v>82</v>
+      </c>
+      <c r="B27" s="15">
         <v>-67547</v>
       </c>
       <c r="C27" s="4">
@@ -1761,19 +1727,19 @@
       <c r="E27">
         <v>296</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="15">
         <v>4077</v>
       </c>
-      <c r="G27" s="13">
+      <c r="G27" s="12">
         <f t="shared" si="1"/>
         <v>6.0357972966971145E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="14">
+        <v>83</v>
+      </c>
+      <c r="B28" s="13">
         <v>-116</v>
       </c>
       <c r="C28">
@@ -1785,19 +1751,19 @@
       <c r="E28">
         <v>2</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="13">
         <v>2</v>
       </c>
-      <c r="G28" s="13">
+      <c r="G28" s="12">
         <f t="shared" si="1"/>
         <v>1.7241379310344827E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="14">
+        <v>84</v>
+      </c>
+      <c r="B29" s="13">
         <v>-827</v>
       </c>
       <c r="C29">
@@ -1809,19 +1775,19 @@
       <c r="E29">
         <v>-2</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F29" s="13">
         <v>-3</v>
       </c>
-      <c r="G29" s="13">
+      <c r="G29" s="12">
         <f t="shared" si="1"/>
         <v>-3.6275695284159614E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="16">
+        <v>85</v>
+      </c>
+      <c r="B30" s="15">
         <v>-14895</v>
       </c>
       <c r="C30">
@@ -1833,17 +1799,17 @@
       <c r="E30">
         <v>19</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="13">
         <v>19</v>
       </c>
-      <c r="G30" s="13">
+      <c r="G30" s="12">
         <f t="shared" si="1"/>
         <v>1.2755958375293723E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1860,240 +1826,240 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="46.140625" customWidth="1"/>
     <col min="2" max="2" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>110</v>
+    <row r="1" spans="1:2">
+      <c r="A1" s="11" t="s">
+        <v>87</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" s="10">
+        <v>88</v>
+      </c>
+      <c r="B2" s="9">
         <f>SourceData!G18</f>
         <v>5.884174667079591E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B3" s="10">
+        <v>89</v>
+      </c>
+      <c r="B3" s="9">
         <f>SourceData!G19</f>
         <v>-0.20980392156862746</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B4" s="11">
+        <v>90</v>
+      </c>
+      <c r="B4" s="10">
         <f>-SUM(SourceData!F20:F21)/SUM(SourceData!B20:B21)</f>
         <v>-0.85572337042925273</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B5" s="10">
+        <v>91</v>
+      </c>
+      <c r="B5" s="9">
         <f>SourceData!G22</f>
         <v>0.81818181818181823</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B6" s="10">
+        <v>92</v>
+      </c>
+      <c r="B6" s="9">
         <f>SourceData!G3</f>
         <v>2.9502480890438512E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B7" s="10">
+        <v>93</v>
+      </c>
+      <c r="B7" s="9">
         <f>SourceData!G5</f>
         <v>9.4637223974763401E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" s="10">
+        <v>94</v>
+      </c>
+      <c r="B8" s="9">
         <f>SourceData!G6</f>
         <v>-1.799775028121485E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>92</v>
-      </c>
-      <c r="B9" s="10">
+        <v>95</v>
+      </c>
+      <c r="B9" s="9">
         <f>SourceData!G7</f>
         <v>9.958401613513173E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B10" s="10">
+        <v>96</v>
+      </c>
+      <c r="B10" s="9">
         <f>SourceData!G8</f>
         <v>8.2506640646175536E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" s="10">
+        <v>97</v>
+      </c>
+      <c r="B11" s="9">
         <f>SourceData!G9</f>
         <v>0.26460159229276781</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" s="10">
+        <v>98</v>
+      </c>
+      <c r="B12" s="9">
         <f>SourceData!G9</f>
         <v>0.26460159229276781</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>96</v>
-      </c>
-      <c r="B13" s="10">
+        <v>99</v>
+      </c>
+      <c r="B13" s="9">
         <f>SourceData!G10</f>
         <v>9.50544015825915E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>97</v>
-      </c>
-      <c r="B14" s="10">
+        <v>100</v>
+      </c>
+      <c r="B14" s="9">
         <f>SourceData!G10</f>
         <v>9.50544015825915E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>98</v>
-      </c>
-      <c r="B15" s="10">
+        <v>101</v>
+      </c>
+      <c r="B15" s="9">
         <f>SourceData!G11</f>
         <v>0.14969670710571925</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B16" s="10">
+        <v>102</v>
+      </c>
+      <c r="B16" s="9">
         <f>SourceData!G12</f>
         <v>0.13454146073585943</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>100</v>
-      </c>
-      <c r="B17" s="10">
+        <v>103</v>
+      </c>
+      <c r="B17" s="9">
         <f>SourceData!G13</f>
         <v>1.1881188118811881E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>101</v>
-      </c>
-      <c r="B18" s="10">
+        <v>104</v>
+      </c>
+      <c r="B18" s="9">
         <f>SourceData!G15</f>
         <v>0.13286713286713286</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>102</v>
-      </c>
-      <c r="B19" s="10">
+        <v>105</v>
+      </c>
+      <c r="B19" s="9">
         <f>SourceData!G15</f>
         <v>0.13286713286713286</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>103</v>
-      </c>
-      <c r="B20" s="10">
+        <v>106</v>
+      </c>
+      <c r="B20" s="9">
         <f>SourceData!G16</f>
         <v>2.0053475935828879E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>104</v>
-      </c>
-      <c r="B21" s="10">
+        <v>107</v>
+      </c>
+      <c r="B21" s="9">
         <f>SourceData!G14</f>
         <v>4.8814504881450485E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>105</v>
-      </c>
-      <c r="B22" s="10">
+        <v>108</v>
+      </c>
+      <c r="B22" s="9">
         <f>SourceData!G14</f>
         <v>4.8814504881450485E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>106</v>
-      </c>
-      <c r="B23" s="10">
+        <v>109</v>
+      </c>
+      <c r="B23" s="9">
         <f>SourceData!G17</f>
         <v>7.2094113727029757E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>107</v>
-      </c>
-      <c r="B24" s="10">
+        <v>110</v>
+      </c>
+      <c r="B24" s="9">
         <f>SourceData!G24</f>
         <v>1.5285845307245491E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B25" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>109</v>
-      </c>
-      <c r="B26" s="20">
+        <v>112</v>
+      </c>
+      <c r="B26">
         <f>SourceData!G25</f>
         <v>0</v>
       </c>
@@ -2102,4 +2068,175 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7B62CD5-8ECB-40A5-A0BE-7FE1423AD32C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C3A689B-497B-454F-989B-DB18A2CB25C5}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57F75511-DB17-413A-81E7-C1945EEC3620}"/>
 </file>